--- a/CGI Fleet Data.xlsx
+++ b/CGI Fleet Data.xlsx
@@ -1,27 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91904\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABDD82F-AA1C-42B3-B933-F1B3B7EB084C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="197">
   <si>
     <t>Truck ID (e.g. CGI-T001)</t>
   </si>
   <si>
-    <t>Branch Registered To</t>
-  </si>
-  <si>
     <t>Registration Number</t>
   </si>
   <si>
@@ -110,13 +113,511 @@
   </si>
   <si>
     <t>Pollution Certificate Expenses</t>
+  </si>
+  <si>
+    <t>TN69AH3722</t>
+  </si>
+  <si>
+    <t>TN69AP3350</t>
+  </si>
+  <si>
+    <t>TN69BH7386</t>
+  </si>
+  <si>
+    <t>TN69AL8092</t>
+  </si>
+  <si>
+    <t>TN69AP6359</t>
+  </si>
+  <si>
+    <t>TN69BA8734</t>
+  </si>
+  <si>
+    <t>TN69BF5772</t>
+  </si>
+  <si>
+    <t>TN69BF5779</t>
+  </si>
+  <si>
+    <t>TN69BF6822</t>
+  </si>
+  <si>
+    <t>TN69BF7548</t>
+  </si>
+  <si>
+    <t>TN69BF3000</t>
+  </si>
+  <si>
+    <t>TN69BJ0366</t>
+  </si>
+  <si>
+    <t>TN69BJ8483</t>
+  </si>
+  <si>
+    <t>TN69BP3199</t>
+  </si>
+  <si>
+    <t>TN04AS3521</t>
+  </si>
+  <si>
+    <t>TN70S0201</t>
+  </si>
+  <si>
+    <t>TN34U8005</t>
+  </si>
+  <si>
+    <t>TN34U8014</t>
+  </si>
+  <si>
+    <t>TN18M8026</t>
+  </si>
+  <si>
+    <t>TN05BZ2381</t>
+  </si>
+  <si>
+    <t>TN69BE0385</t>
+  </si>
+  <si>
+    <t>TN69BE5910</t>
+  </si>
+  <si>
+    <t>TN69BL5448</t>
+  </si>
+  <si>
+    <t>TN69BD5431</t>
+  </si>
+  <si>
+    <t>TN69BE0397</t>
+  </si>
+  <si>
+    <t>TN69BE0407</t>
+  </si>
+  <si>
+    <t>TN69BE5846</t>
+  </si>
+  <si>
+    <t>TN87C5358</t>
+  </si>
+  <si>
+    <t>TN69BS7411</t>
+  </si>
+  <si>
+    <t>TN69BU5325</t>
+  </si>
+  <si>
+    <t>TN69BU5337</t>
+  </si>
+  <si>
+    <t>TN69BU5614</t>
+  </si>
+  <si>
+    <t>TN69BU5720</t>
+  </si>
+  <si>
+    <t>TN69BU5736</t>
+  </si>
+  <si>
+    <t>TN69BW0765</t>
+  </si>
+  <si>
+    <t>TN69BW0775</t>
+  </si>
+  <si>
+    <t>TN69BW4901</t>
+  </si>
+  <si>
+    <t>TN69BW4920</t>
+  </si>
+  <si>
+    <t>TN88L4509</t>
+  </si>
+  <si>
+    <t>TN47BY8131</t>
+  </si>
+  <si>
+    <t>TN04AU1653</t>
+  </si>
+  <si>
+    <t>TN93C3377</t>
+  </si>
+  <si>
+    <t>Branch Assigned To</t>
+  </si>
+  <si>
+    <t>TUTICORIN</t>
+  </si>
+  <si>
+    <t>CHENNAI</t>
+  </si>
+  <si>
+    <t>TATA MOTORS LTD</t>
+  </si>
+  <si>
+    <t>BHARATBENZ</t>
+  </si>
+  <si>
+    <t>TATA LPT</t>
+  </si>
+  <si>
+    <t>EICHER</t>
+  </si>
+  <si>
+    <t>ASHOK LEYLAND LTD</t>
+  </si>
+  <si>
+    <t>EICHER MOTORS</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>TATA SIGNA</t>
+  </si>
+  <si>
+    <t>RIGID-20</t>
+  </si>
+  <si>
+    <t>ARTICULATED-40</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2027-05-29</t>
+  </si>
+  <si>
+    <t>2027-02-26</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2027-03-08</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>2027-04-08</t>
+  </si>
+  <si>
+    <t>2026-11-10</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2027-02-13</t>
+  </si>
+  <si>
+    <t>2026-12-04</t>
+  </si>
+  <si>
+    <t>2027-03-04</t>
+  </si>
+  <si>
+    <t>2026-10-18</t>
+  </si>
+  <si>
+    <t>2027-02-24</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2027-06-13</t>
+  </si>
+  <si>
+    <t>2027-03-13</t>
+  </si>
+  <si>
+    <t>2027-02-02</t>
+  </si>
+  <si>
+    <t>2027-03-02</t>
+  </si>
+  <si>
+    <t>2026-12-16</t>
+  </si>
+  <si>
+    <t>2027-03-26</t>
+  </si>
+  <si>
+    <t>2027-04-02</t>
+  </si>
+  <si>
+    <t>2012-12-27</t>
+  </si>
+  <si>
+    <t>2006-11-15</t>
+  </si>
+  <si>
+    <t>2019-03-22</t>
+  </si>
+  <si>
+    <t>2009-03-14</t>
+  </si>
+  <si>
+    <t>2015-05-31</t>
+  </si>
+  <si>
+    <t>2004-11-16</t>
+  </si>
+  <si>
+    <t>2009-06-18</t>
+  </si>
+  <si>
+    <t>2019-09-24</t>
+  </si>
+  <si>
+    <t>2010-08-18</t>
+  </si>
+  <si>
+    <t>2018-11-20</t>
+  </si>
+  <si>
+    <t>2019-05-16</t>
+  </si>
+  <si>
+    <t>2019-10-03</t>
+  </si>
+  <si>
+    <t>2021-11-17</t>
+  </si>
+  <si>
+    <t>2001-11-17</t>
+  </si>
+  <si>
+    <t>2016-01-12</t>
+  </si>
+  <si>
+    <t>2019-08-21</t>
+  </si>
+  <si>
+    <t>2014-08-21</t>
+  </si>
+  <si>
+    <t>2012-12-12</t>
+  </si>
+  <si>
+    <t>2020-01-24</t>
+  </si>
+  <si>
+    <t>2017-12-11</t>
+  </si>
+  <si>
+    <t>2018-03-21</t>
+  </si>
+  <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
+    <t>2017-08-24</t>
+  </si>
+  <si>
+    <t>2012-05-23</t>
+  </si>
+  <si>
+    <t>2023-08-18</t>
+  </si>
+  <si>
+    <t>2024-06-25</t>
+  </si>
+  <si>
+    <t>2024-06-28</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>2025-05-13</t>
+  </si>
+  <si>
+    <t>2022-04-27</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>2018-03-19</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2027-08-08</t>
+  </si>
+  <si>
+    <t>2026-12-23</t>
+  </si>
+  <si>
+    <t>2027-02-22</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>2026-11-11</t>
+  </si>
+  <si>
+    <t>2026-10-25</t>
+  </si>
+  <si>
+    <t>2026-11-24</t>
+  </si>
+  <si>
+    <t>2027-08-14</t>
+  </si>
+  <si>
+    <t>2019-01-11</t>
+  </si>
+  <si>
+    <t>2026-11-26</t>
+  </si>
+  <si>
+    <t>2026-12-30</t>
+  </si>
+  <si>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>2028-02-24</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2027-08-17</t>
+  </si>
+  <si>
+    <t>2027-01-10</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2027-07-05</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2027-05-06</t>
+  </si>
+  <si>
+    <t>2027-03-06</t>
+  </si>
+  <si>
+    <t>2027-05-12</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>2027-04-26</t>
+  </si>
+  <si>
+    <t>2028-04-28</t>
+  </si>
+  <si>
+    <t>09901</t>
+  </si>
+  <si>
+    <t>05966</t>
+  </si>
+  <si>
+    <t>03133</t>
+  </si>
+  <si>
+    <t>A9686</t>
+  </si>
+  <si>
+    <t>J0158</t>
+  </si>
+  <si>
+    <t>V0033</t>
+  </si>
+  <si>
+    <t>04145</t>
+  </si>
+  <si>
+    <t>09358</t>
+  </si>
+  <si>
+    <t>09279</t>
+  </si>
+  <si>
+    <t>09359</t>
+  </si>
+  <si>
+    <t>09446</t>
+  </si>
+  <si>
+    <t>D6543</t>
+  </si>
+  <si>
+    <t>D6638</t>
+  </si>
+  <si>
+    <t>D6539</t>
+  </si>
+  <si>
+    <t>300 to 365</t>
+  </si>
+  <si>
+    <t>215 to 380</t>
+  </si>
+  <si>
+    <t>330 to 380</t>
+  </si>
+  <si>
+    <t>300 to 375</t>
+  </si>
+  <si>
+    <t>365 to 557</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,10 +669,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -179,13 +687,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -223,7 +739,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -257,6 +773,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -291,9 +808,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -466,106 +984,1346 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="25" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:32" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
         <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2">
+        <v>20894</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M2" t="s">
+        <v>110</v>
+      </c>
+      <c r="P2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3">
+        <v>16520</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="M3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4">
+        <v>28326</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M4" t="s">
+        <v>112</v>
+      </c>
+      <c r="P4" t="s">
+        <v>88</v>
+      </c>
+      <c r="V4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M5" t="s">
+        <v>113</v>
+      </c>
+      <c r="P5" t="s">
+        <v>86</v>
+      </c>
+      <c r="V5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P6" t="s">
+        <v>89</v>
+      </c>
+      <c r="V6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P7" t="s">
+        <v>90</v>
+      </c>
+      <c r="V7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8">
+        <v>65324</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M8" t="s">
+        <v>116</v>
+      </c>
+      <c r="P8" t="s">
+        <v>86</v>
+      </c>
+      <c r="V8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9">
+        <v>65304</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M9" t="s">
+        <v>116</v>
+      </c>
+      <c r="P9" t="s">
+        <v>86</v>
+      </c>
+      <c r="V9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10">
+        <v>65410</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M10" t="s">
+        <v>117</v>
+      </c>
+      <c r="P10" t="s">
+        <v>91</v>
+      </c>
+      <c r="V10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11">
+        <v>23502</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M11" t="s">
+        <v>118</v>
+      </c>
+      <c r="P11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12">
+        <v>55907</v>
+      </c>
+      <c r="J12" s="4">
+        <v>350</v>
+      </c>
+      <c r="M12" t="s">
+        <v>119</v>
+      </c>
+      <c r="P12" t="s">
+        <v>93</v>
+      </c>
+      <c r="V12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" t="s">
+        <v>181</v>
+      </c>
+      <c r="J13" s="4">
+        <v>375</v>
+      </c>
+      <c r="M13" t="s">
+        <v>120</v>
+      </c>
+      <c r="P13" t="s">
+        <v>94</v>
+      </c>
+      <c r="V13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14">
+        <v>12646</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M14" t="s">
+        <v>121</v>
+      </c>
+      <c r="P14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15">
+        <v>11442</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M15" t="s">
+        <v>122</v>
+      </c>
+      <c r="P15" t="s">
+        <v>95</v>
+      </c>
+      <c r="V15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16">
+        <v>20548</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M16" t="s">
+        <v>123</v>
+      </c>
+      <c r="P16" t="s">
+        <v>86</v>
+      </c>
+      <c r="V16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17">
+        <v>24298</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M17" t="s">
+        <v>124</v>
+      </c>
+      <c r="P17" t="s">
+        <v>86</v>
+      </c>
+      <c r="V17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18">
+        <v>82520</v>
+      </c>
+      <c r="J18" s="4">
+        <v>375</v>
+      </c>
+      <c r="M18" t="s">
+        <v>125</v>
+      </c>
+      <c r="P18" t="s">
+        <v>86</v>
+      </c>
+      <c r="V18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19">
+        <v>82624</v>
+      </c>
+      <c r="J19" s="4">
+        <v>375</v>
+      </c>
+      <c r="M19" t="s">
+        <v>126</v>
+      </c>
+      <c r="P19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" t="s">
+        <v>182</v>
+      </c>
+      <c r="J20" s="4">
+        <v>375</v>
+      </c>
+      <c r="M20" t="s">
+        <v>127</v>
+      </c>
+      <c r="P20" t="s">
+        <v>96</v>
+      </c>
+      <c r="V20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21">
+        <v>90103</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M21" t="s">
+        <v>128</v>
+      </c>
+      <c r="P21" t="s">
+        <v>97</v>
+      </c>
+      <c r="V21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22">
+        <v>51017</v>
+      </c>
+      <c r="J22" s="4">
+        <v>455</v>
+      </c>
+      <c r="M22" t="s">
+        <v>129</v>
+      </c>
+      <c r="P22" t="s">
+        <v>98</v>
+      </c>
+      <c r="V22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23">
+        <v>51902</v>
+      </c>
+      <c r="J23" s="4">
+        <v>455</v>
+      </c>
+      <c r="M23" t="s">
+        <v>130</v>
+      </c>
+      <c r="P23" t="s">
+        <v>99</v>
+      </c>
+      <c r="V23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" t="s">
+        <v>183</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="M24" t="s">
+        <v>131</v>
+      </c>
+      <c r="P24" t="s">
+        <v>100</v>
+      </c>
+      <c r="V24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25">
+        <v>45236</v>
+      </c>
+      <c r="J25" s="4">
+        <v>455</v>
+      </c>
+      <c r="M25" t="s">
+        <v>132</v>
+      </c>
+      <c r="P25" t="s">
+        <v>86</v>
+      </c>
+      <c r="V25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26">
+        <v>51861</v>
+      </c>
+      <c r="J26" s="4">
+        <v>455</v>
+      </c>
+      <c r="M26" t="s">
+        <v>129</v>
+      </c>
+      <c r="P26" t="s">
+        <v>98</v>
+      </c>
+      <c r="V26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27">
+        <v>51049</v>
+      </c>
+      <c r="J27" s="4">
+        <v>455</v>
+      </c>
+      <c r="M27" t="s">
+        <v>129</v>
+      </c>
+      <c r="P27" t="s">
+        <v>98</v>
+      </c>
+      <c r="V27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28">
+        <v>51925</v>
+      </c>
+      <c r="J28" s="4">
+        <v>455</v>
+      </c>
+      <c r="M28" t="s">
+        <v>130</v>
+      </c>
+      <c r="P28" t="s">
+        <v>86</v>
+      </c>
+      <c r="V28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M29" t="s">
+        <v>133</v>
+      </c>
+      <c r="P29" t="s">
+        <v>101</v>
+      </c>
+      <c r="V29" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30">
+        <v>39409</v>
+      </c>
+      <c r="J30" s="4">
+        <v>455</v>
+      </c>
+      <c r="M30" t="s">
+        <v>134</v>
+      </c>
+      <c r="P30" t="s">
+        <v>102</v>
+      </c>
+      <c r="V30" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="M31" t="s">
+        <v>135</v>
+      </c>
+      <c r="P31" t="s">
+        <v>103</v>
+      </c>
+      <c r="V31" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="M32" t="s">
+        <v>135</v>
+      </c>
+      <c r="P32" t="s">
+        <v>103</v>
+      </c>
+      <c r="V32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" t="s">
+        <v>77</v>
+      </c>
+      <c r="F33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="3">
+        <v>49774</v>
+      </c>
+      <c r="J33" s="4">
+        <v>455</v>
+      </c>
+      <c r="M33" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" t="s">
+        <v>103</v>
+      </c>
+      <c r="V33" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" t="s">
+        <v>83</v>
+      </c>
+      <c r="F34" t="s">
+        <v>85</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="M34" t="s">
+        <v>137</v>
+      </c>
+      <c r="P34" t="s">
+        <v>104</v>
+      </c>
+      <c r="V34" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" t="s">
+        <v>83</v>
+      </c>
+      <c r="F35" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="M35" t="s">
+        <v>137</v>
+      </c>
+      <c r="P35" t="s">
+        <v>103</v>
+      </c>
+      <c r="V35" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" t="s">
+        <v>189</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="M36" t="s">
+        <v>138</v>
+      </c>
+      <c r="P36" t="s">
+        <v>105</v>
+      </c>
+      <c r="V36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F37" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" t="s">
+        <v>190</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="M37" t="s">
+        <v>138</v>
+      </c>
+      <c r="P37" t="s">
+        <v>105</v>
+      </c>
+      <c r="V37" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" t="s">
+        <v>85</v>
+      </c>
+      <c r="G38">
+        <v>48785</v>
+      </c>
+      <c r="J38" s="4">
+        <v>455</v>
+      </c>
+      <c r="M38" t="s">
+        <v>139</v>
+      </c>
+      <c r="P38" t="s">
+        <v>106</v>
+      </c>
+      <c r="V38" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" t="s">
+        <v>191</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="M39" t="s">
+        <v>139</v>
+      </c>
+      <c r="P39" t="s">
+        <v>105</v>
+      </c>
+      <c r="V39" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" t="s">
+        <v>84</v>
+      </c>
+      <c r="J40" s="4">
+        <v>375</v>
+      </c>
+      <c r="M40" t="s">
+        <v>140</v>
+      </c>
+      <c r="P40" t="s">
+        <v>107</v>
+      </c>
+      <c r="V40" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" t="s">
+        <v>80</v>
+      </c>
+      <c r="F41" t="s">
+        <v>84</v>
+      </c>
+      <c r="J41" s="4">
+        <v>375</v>
+      </c>
+      <c r="M41" t="s">
+        <v>141</v>
+      </c>
+      <c r="P41" t="s">
+        <v>108</v>
+      </c>
+      <c r="V41" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" t="s">
+        <v>84</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M42" t="s">
+        <v>142</v>
+      </c>
+      <c r="P42" t="s">
+        <v>104</v>
+      </c>
+      <c r="V42" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" t="s">
+        <v>84</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M43" t="s">
+        <v>143</v>
+      </c>
+      <c r="P43" t="s">
+        <v>109</v>
+      </c>
+      <c r="V43" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
